--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -128,12 +128,12 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
@@ -161,18 +161,57 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>GUTIERREZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>PEÑA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>RIVADENEYRA</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>PEDRO ANGEL</t>
+  </si>
+  <si>
+    <t>MILKA SARAY</t>
+  </si>
+  <si>
+    <t>ALBERTO SHAKIB</t>
+  </si>
+  <si>
+    <t>OLIVER ULISES</t>
+  </si>
+  <si>
+    <t>RONALDO</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
+  </si>
+  <si>
     <t>CABRERA</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GUTIERREZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
@@ -182,24 +221,12 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>PEÑA</t>
-  </si>
-  <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
     <t>REYES</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
     <t>TEMOXTLE</t>
   </si>
   <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
     <t>TREJO</t>
   </si>
   <si>
@@ -209,21 +236,12 @@
     <t>ILLESCAS</t>
   </si>
   <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
     <t>SANTOS</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
-    <t>RIVADENEYRA</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
     <t>GALICIA</t>
   </si>
   <si>
@@ -233,24 +251,15 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>PEDRO ANGEL</t>
-  </si>
-  <si>
     <t>JOSE RUBEN</t>
   </si>
   <si>
     <t>CRISTHIAN ALFONSO</t>
   </si>
   <si>
-    <t>MILKA SARAY</t>
-  </si>
-  <si>
     <t>REDA ALAN</t>
   </si>
   <si>
-    <t>ALBERTO SHAKIB</t>
-  </si>
-  <si>
     <t>ANGEL GABRIEL</t>
   </si>
   <si>
@@ -260,19 +269,10 @@
     <t>DAVID</t>
   </si>
   <si>
-    <t>OLIVER ULISES</t>
-  </si>
-  <si>
-    <t>RONALDO</t>
-  </si>
-  <si>
     <t>ROGELIO</t>
   </si>
   <si>
     <t>LUIS ANGEL</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -764,7 +764,7 @@
         <v>6</v>
       </c>
       <c r="C4">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D4">
         <v>5</v>
@@ -773,13 +773,13 @@
         <v>6</v>
       </c>
       <c r="F4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G4">
         <v>-1</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>-1</v>
@@ -788,10 +788,10 @@
         <v>-1</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
         <v>-1</v>
@@ -815,19 +815,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V4">
         <v>5</v>
       </c>
       <c r="W4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="X4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>-1</v>
@@ -841,7 +841,7 @@
         <v>10</v>
       </c>
       <c r="C5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>9</v>
@@ -856,7 +856,7 @@
         <v>6</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I5">
         <v>-1</v>
@@ -865,13 +865,13 @@
         <v>-1</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -895,19 +895,19 @@
         <v>10</v>
       </c>
       <c r="U5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V5">
         <v>9</v>
       </c>
       <c r="W5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y5">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -918,7 +918,7 @@
         <v>9</v>
       </c>
       <c r="C6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="D6">
         <v>6</v>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I6">
         <v>-1</v>
@@ -942,13 +942,13 @@
         <v>-1</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -972,19 +972,19 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X6">
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -995,7 +995,7 @@
         <v>10</v>
       </c>
       <c r="C7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D7">
         <v>5</v>
@@ -1010,7 +1010,7 @@
         <v>-1</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>-1</v>
@@ -1022,7 +1022,7 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
         <v>-1</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V7">
         <v>5</v>
@@ -1058,7 +1058,7 @@
         <v>-1</v>
       </c>
       <c r="X7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y7">
         <v>-1</v>
@@ -1072,7 +1072,7 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D8">
         <v>8</v>
@@ -1087,7 +1087,7 @@
         <v>10</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I8">
         <v>-1</v>
@@ -1096,13 +1096,13 @@
         <v>-1</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1126,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V8">
         <v>8</v>
@@ -1149,7 +1149,7 @@
         <v>6</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D9">
         <v>5</v>
@@ -1164,7 +1164,7 @@
         <v>-1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I9">
         <v>-1</v>
@@ -1173,10 +1173,10 @@
         <v>-1</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1200,19 +1200,19 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V9">
         <v>5</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y9">
         <v>-1</v>
@@ -1226,7 +1226,7 @@
         <v>7</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>8</v>
@@ -1241,7 +1241,7 @@
         <v>6</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I10">
         <v>-1</v>
@@ -1250,13 +1250,13 @@
         <v>-1</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1280,19 +1280,19 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>8</v>
       </c>
       <c r="W10">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="X10">
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1303,7 +1303,7 @@
         <v>7</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D11">
         <v>5</v>
@@ -1318,7 +1318,7 @@
         <v>10</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>-1</v>
@@ -1327,13 +1327,13 @@
         <v>-1</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1354,10 +1354,10 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1369,7 +1369,7 @@
         <v>10</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1380,7 +1380,7 @@
         <v>10</v>
       </c>
       <c r="C12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D12">
         <v>9</v>
@@ -1395,7 +1395,7 @@
         <v>6</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>-1</v>
@@ -1404,13 +1404,13 @@
         <v>-1</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1434,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>9</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1457,7 +1457,7 @@
         <v>9</v>
       </c>
       <c r="C13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D13">
         <v>5</v>
@@ -1472,7 +1472,7 @@
         <v>-1</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I13">
         <v>-1</v>
@@ -1481,10 +1481,10 @@
         <v>-1</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
         <v>-1</v>
@@ -1508,10 +1508,10 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1520,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y13">
         <v>-1</v>
@@ -1534,7 +1534,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D14">
         <v>5</v>
@@ -1543,13 +1543,13 @@
         <v>5</v>
       </c>
       <c r="F14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G14">
         <v>-1</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1558,10 +1558,10 @@
         <v>-1</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1585,10 +1585,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1597,7 +1597,7 @@
         <v>5</v>
       </c>
       <c r="X14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Y14">
         <v>-1</v>
@@ -1611,7 +1611,7 @@
         <v>7</v>
       </c>
       <c r="C15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="D15">
         <v>5</v>
@@ -1626,7 +1626,7 @@
         <v>6</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I15">
         <v>-1</v>
@@ -1635,13 +1635,13 @@
         <v>-1</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1662,10 +1662,10 @@
         <v>-1</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1674,10 +1674,10 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1688,7 +1688,7 @@
         <v>10</v>
       </c>
       <c r="C16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D16">
         <v>9</v>
@@ -1703,7 +1703,7 @@
         <v>6</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
         <v>-1</v>
@@ -1712,13 +1712,13 @@
         <v>-1</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1765,7 +1765,7 @@
         <v>5</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="D17">
         <v>5</v>
@@ -1774,13 +1774,13 @@
         <v>5</v>
       </c>
       <c r="F17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="G17">
         <v>-1</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I17">
         <v>-1</v>
@@ -1789,10 +1789,10 @@
         <v>-1</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M17">
         <v>-1</v>
@@ -1816,10 +1816,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1828,7 +1828,7 @@
         <v>5</v>
       </c>
       <c r="X17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Y17">
         <v>-1</v>
@@ -1842,7 +1842,7 @@
         <v>9</v>
       </c>
       <c r="C18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="D18">
         <v>6</v>
@@ -1857,7 +1857,7 @@
         <v>7</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
         <v>-1</v>
@@ -1866,13 +1866,13 @@
         <v>-1</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -1893,22 +1893,22 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="V18">
         <v>6</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -1973,27 +1973,30 @@
         <v>15</v>
       </c>
       <c r="D2">
+        <v>7</v>
+      </c>
+      <c r="E2">
+        <v>8</v>
+      </c>
+      <c r="F2">
+        <v>46.67</v>
+      </c>
+      <c r="G2">
+        <v>53.33</v>
+      </c>
+      <c r="H2">
+        <v>6.3</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2">
         <v>0</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
-      <c r="G2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>15</v>
-      </c>
-      <c r="J2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -2002,19 +2005,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>46.67</v>
+        <v>60</v>
       </c>
       <c r="G3">
-        <v>53.33</v>
+        <v>40</v>
       </c>
       <c r="H3">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2046,7 +2049,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="I4">
         <v>6</v>
@@ -2066,19 +2069,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F5">
-        <v>73.33</v>
+        <v>66.67</v>
       </c>
       <c r="G5">
-        <v>20</v>
+        <v>26.67</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="I5">
         <v>1</v>
@@ -2098,25 +2101,25 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>93.33</v>
+      </c>
+      <c r="G6">
+        <v>6.67</v>
+      </c>
+      <c r="H6">
+        <v>8.9</v>
+      </c>
+      <c r="I6">
         <v>0</v>
       </c>
-      <c r="F6">
-        <v>80</v>
-      </c>
-      <c r="G6">
+      <c r="J6">
         <v>0</v>
-      </c>
-      <c r="H6">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="I6">
-        <v>3</v>
-      </c>
-      <c r="J6">
-        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -2130,19 +2133,19 @@
         <v>15</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>86.67</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>13.33</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2158,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2193,30 +2196,30 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -2227,462 +2230,102 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920138</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C5" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920139</v>
+        <v>21330051920395</v>
       </c>
       <c r="B6" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C6" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="E6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920140</v>
+        <v>21330051920147</v>
       </c>
       <c r="B7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>74</v>
+        <v>61</v>
       </c>
       <c r="E7" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
       </c>
       <c r="D8" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>21330051920140</v>
-      </c>
-      <c r="B9" t="s">
-        <v>49</v>
-      </c>
-      <c r="C9" t="s">
-        <v>48</v>
-      </c>
-      <c r="D9" t="s">
-        <v>74</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>21330051650295</v>
-      </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>21330051920141</v>
-      </c>
-      <c r="B11" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" t="s">
-        <v>63</v>
-      </c>
-      <c r="D11" t="s">
-        <v>76</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>21330051920141</v>
-      </c>
-      <c r="B12" t="s">
-        <v>50</v>
-      </c>
-      <c r="C12" t="s">
-        <v>63</v>
-      </c>
-      <c r="D12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>21330051920143</v>
-      </c>
-      <c r="B13" t="s">
-        <v>51</v>
-      </c>
-      <c r="C13" t="s">
-        <v>64</v>
-      </c>
-      <c r="D13" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>21330051920145</v>
-      </c>
-      <c r="B14" t="s">
-        <v>52</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
-      </c>
-      <c r="D14" t="s">
-        <v>78</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>21330051920146</v>
-      </c>
-      <c r="B15" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" t="s">
-        <v>65</v>
-      </c>
-      <c r="D15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E15" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>21330051920395</v>
-      </c>
-      <c r="B16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C16" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" t="s">
-        <v>80</v>
-      </c>
-      <c r="E16" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>21330051920395</v>
-      </c>
-      <c r="B17" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E17" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>21330051920147</v>
-      </c>
-      <c r="B18" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" t="s">
-        <v>67</v>
-      </c>
-      <c r="D18" t="s">
-        <v>81</v>
-      </c>
-      <c r="E18" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>21330051920147</v>
-      </c>
-      <c r="B19" t="s">
-        <v>55</v>
-      </c>
-      <c r="C19" t="s">
-        <v>67</v>
-      </c>
-      <c r="D19" t="s">
-        <v>81</v>
-      </c>
-      <c r="E19" t="s">
-        <v>10</v>
-      </c>
-      <c r="F19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>21330051920147</v>
-      </c>
-      <c r="B20" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" t="s">
-        <v>67</v>
-      </c>
-      <c r="D20" t="s">
-        <v>81</v>
-      </c>
-      <c r="E20" t="s">
-        <v>9</v>
-      </c>
-      <c r="F20" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>21330051920148</v>
-      </c>
-      <c r="B21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C21" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" t="s">
-        <v>82</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>21330051920150</v>
-      </c>
-      <c r="B22" t="s">
-        <v>56</v>
-      </c>
-      <c r="C22" t="s">
-        <v>69</v>
-      </c>
-      <c r="D22" t="s">
-        <v>83</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>21330051920382</v>
-      </c>
-      <c r="B23" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" t="s">
-        <v>84</v>
-      </c>
-      <c r="E23" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>21330051920382</v>
-      </c>
-      <c r="B24" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" t="s">
-        <v>50</v>
-      </c>
-      <c r="D24" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" t="s">
-        <v>10</v>
-      </c>
-      <c r="F24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>21330051920382</v>
-      </c>
-      <c r="B25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" t="s">
-        <v>84</v>
-      </c>
-      <c r="E25" t="s">
-        <v>9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>21330051920392</v>
-      </c>
-      <c r="B26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -2718,104 +2361,104 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920147</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="E4">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920382</v>
+        <v>21330051920395</v>
       </c>
       <c r="B5" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>60</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>61</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920395</v>
+        <v>21330051920382</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -2823,16 +2466,16 @@
         <v>21330051920138</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="C8" t="s">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="D8" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -2840,16 +2483,16 @@
         <v>21330051920139</v>
       </c>
       <c r="B9" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C9" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="D9" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -2857,16 +2500,16 @@
         <v>21330051650295</v>
       </c>
       <c r="B10" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C10" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -2874,16 +2517,16 @@
         <v>21330051920143</v>
       </c>
       <c r="B11" t="s">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C11" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -2891,16 +2534,16 @@
         <v>21330051920145</v>
       </c>
       <c r="B12" t="s">
-        <v>52</v>
+        <v>65</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D12" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -2908,16 +2551,16 @@
         <v>21330051920146</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>66</v>
       </c>
       <c r="C13" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
@@ -2925,16 +2568,16 @@
         <v>21330051920148</v>
       </c>
       <c r="B14" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:5">
@@ -2942,16 +2585,16 @@
         <v>21330051920150</v>
       </c>
       <c r="B15" t="s">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="C15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:5">
@@ -2959,16 +2602,16 @@
         <v>21330051920392</v>
       </c>
       <c r="B16" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C16" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="D16" t="s">
         <v>85</v>
       </c>
       <c r="E16">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2978,7 +2621,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3010,45 +2653,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>21330051920148</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -3056,209 +2699,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920148</v>
+        <v>21330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>56</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>21330051920148</v>
-      </c>
-      <c r="B5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C5" t="s">
-        <v>68</v>
-      </c>
-      <c r="D5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" t="s">
-        <v>7</v>
-      </c>
-      <c r="F5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920138</v>
-      </c>
-      <c r="B6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920139</v>
-      </c>
-      <c r="B7" t="s">
-        <v>48</v>
-      </c>
-      <c r="C7" t="s">
-        <v>61</v>
-      </c>
-      <c r="D7" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051650295</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>62</v>
-      </c>
-      <c r="D8" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920143</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920146</v>
-      </c>
-      <c r="B10" t="s">
-        <v>53</v>
-      </c>
-      <c r="C10" t="s">
-        <v>65</v>
-      </c>
-      <c r="D10" t="s">
-        <v>79</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920150</v>
-      </c>
-      <c r="B11" t="s">
-        <v>56</v>
-      </c>
-      <c r="C11" t="s">
-        <v>69</v>
-      </c>
-      <c r="D11" t="s">
-        <v>83</v>
-      </c>
-      <c r="E11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920392</v>
-      </c>
-      <c r="B12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C12" t="s">
-        <v>70</v>
-      </c>
-      <c r="D12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>36</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -785,7 +785,7 @@
         <v>-1</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -862,7 +862,7 @@
         <v>-1</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K5">
         <v>9</v>
@@ -898,7 +898,7 @@
         <v>9</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -939,7 +939,7 @@
         <v>-1</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K6">
         <v>10</v>
@@ -1016,7 +1016,7 @@
         <v>-1</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>-1</v>
@@ -1093,7 +1093,7 @@
         <v>-1</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K8">
         <v>9</v>
@@ -1129,7 +1129,7 @@
         <v>6</v>
       </c>
       <c r="V8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W8">
         <v>9</v>
@@ -1170,7 +1170,7 @@
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1247,7 +1247,7 @@
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K10">
         <v>7</v>
@@ -1283,7 +1283,7 @@
         <v>6</v>
       </c>
       <c r="V10">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>7</v>
@@ -1324,7 +1324,7 @@
         <v>-1</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1401,7 +1401,7 @@
         <v>-1</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K12">
         <v>8</v>
@@ -1437,7 +1437,7 @@
         <v>8</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>9</v>
@@ -1478,7 +1478,7 @@
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K13">
         <v>6</v>
@@ -1555,7 +1555,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>6</v>
@@ -1632,7 +1632,7 @@
         <v>-1</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
         <v>7</v>
@@ -1709,7 +1709,7 @@
         <v>-1</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
         <v>8</v>
@@ -1786,7 +1786,7 @@
         <v>-1</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K17">
         <v>6</v>
@@ -1863,7 +1863,7 @@
         <v>-1</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K18">
         <v>10</v>
@@ -1985,7 +1985,7 @@
         <v>53.33</v>
       </c>
       <c r="H2">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
         <v>0</v>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -782,7 +782,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -859,7 +859,7 @@
         <v>9</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
         <v>10</v>
@@ -936,7 +936,7 @@
         <v>9</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J6">
         <v>6</v>
@@ -972,7 +972,7 @@
         <v>9</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>6</v>
@@ -1013,7 +1013,7 @@
         <v>9</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J7">
         <v>5</v>
@@ -1090,7 +1090,7 @@
         <v>9</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
         <v>6</v>
@@ -1126,7 +1126,7 @@
         <v>10</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>7</v>
@@ -1167,7 +1167,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J9">
         <v>6</v>
@@ -1244,7 +1244,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J10">
         <v>6</v>
@@ -1280,7 +1280,7 @@
         <v>7</v>
       </c>
       <c r="U10">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1321,7 +1321,7 @@
         <v>5</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J11">
         <v>5</v>
@@ -1357,7 +1357,7 @@
         <v>6</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1398,7 +1398,7 @@
         <v>9</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>6</v>
@@ -1434,7 +1434,7 @@
         <v>10</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1475,7 +1475,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>5</v>
@@ -1511,7 +1511,7 @@
         <v>8</v>
       </c>
       <c r="U13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V13">
         <v>5</v>
@@ -1552,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
@@ -1629,7 +1629,7 @@
         <v>10</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>6</v>
@@ -1665,7 +1665,7 @@
         <v>9</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V15">
         <v>5</v>
@@ -1706,7 +1706,7 @@
         <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
         <v>9</v>
@@ -1742,7 +1742,7 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1783,7 +1783,7 @@
         <v>8</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J17">
         <v>5</v>
@@ -1860,7 +1860,7 @@
         <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J18">
         <v>6</v>
@@ -2005,16 +2005,16 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>60</v>
+        <v>53.33</v>
       </c>
       <c r="G3">
-        <v>40</v>
+        <v>46.67</v>
       </c>
       <c r="H3">
         <v>6.4</v>
@@ -2621,7 +2621,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2653,16 +2653,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920148</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -2676,16 +2676,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920148</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -2699,24 +2699,47 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920145</v>
+        <v>21330051920143</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4" t="s">
+        <v>37</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>21330051920148</v>
+      </c>
+      <c r="B5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
+      </c>
+      <c r="F5" t="s">
         <v>36</v>
       </c>
-      <c r="G4">
+      <c r="G5">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -1001,7 +1001,7 @@
         <v>5</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="F7">
         <v>9</v>
@@ -1019,7 +1019,7 @@
         <v>5</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L7">
         <v>10</v>
@@ -1055,7 +1055,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -2069,25 +2069,25 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5">
         <v>4</v>
       </c>
       <c r="F5">
-        <v>66.67</v>
+        <v>73.33</v>
       </c>
       <c r="G5">
         <v>26.67</v>
       </c>
       <c r="H5">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>6.67</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -2161,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2230,36 +2230,36 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D4" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>21330051920141</v>
+        <v>21330051920395</v>
       </c>
       <c r="B5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D5" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -2270,16 +2270,16 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>21330051920395</v>
+        <v>21330051920147</v>
       </c>
       <c r="B6" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D6" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -2290,41 +2290,21 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
       </c>
       <c r="F7" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>21330051920382</v>
-      </c>
-      <c r="B8" t="s">
-        <v>51</v>
-      </c>
-      <c r="C8" t="s">
-        <v>48</v>
-      </c>
-      <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2361,33 +2341,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E3">
         <v>1</v>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -134,12 +134,12 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
@@ -161,118 +161,118 @@
     <t>ALVAREZ</t>
   </si>
   <si>
+    <t>CABRERA</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>GUTIERREZ</t>
   </si>
   <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>PEÑA</t>
   </si>
   <si>
     <t>RAMIREZ</t>
   </si>
   <si>
+    <t>REYES</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>TEMOXTLE</t>
+  </si>
+  <si>
     <t>RIVERA</t>
   </si>
   <si>
-    <t>FLORES</t>
+    <t>TREJO</t>
+  </si>
+  <si>
+    <t>MIXCOHA</t>
+  </si>
+  <si>
+    <t>ILLESCAS</t>
   </si>
   <si>
     <t>NAJERA</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
     <t>RIVADENEYRA</t>
   </si>
   <si>
     <t>GOMEZ</t>
   </si>
   <si>
+    <t>GALICIA</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>PEDRO ANGEL</t>
   </si>
   <si>
+    <t>JOSE RUBEN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN ALFONSO</t>
+  </si>
+  <si>
     <t>MILKA SARAY</t>
   </si>
   <si>
+    <t>REDA ALAN</t>
+  </si>
+  <si>
     <t>ALBERTO SHAKIB</t>
   </si>
   <si>
+    <t>ANGEL GABRIEL</t>
+  </si>
+  <si>
+    <t>ALEXIS ISAI</t>
+  </si>
+  <si>
+    <t>DAVID</t>
+  </si>
+  <si>
     <t>OLIVER ULISES</t>
   </si>
   <si>
     <t>RONALDO</t>
   </si>
   <si>
+    <t>ROGELIO</t>
+  </si>
+  <si>
+    <t>LUIS ANGEL</t>
+  </si>
+  <si>
     <t>LUIS GUILLERMO</t>
-  </si>
-  <si>
-    <t>CABRERA</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>TEMOXTLE</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>MIXCOHA</t>
-  </si>
-  <si>
-    <t>ILLESCAS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>GALICIA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JOSE RUBEN</t>
-  </si>
-  <si>
-    <t>CRISTHIAN ALFONSO</t>
-  </si>
-  <si>
-    <t>REDA ALAN</t>
-  </si>
-  <si>
-    <t>ANGEL GABRIEL</t>
-  </si>
-  <si>
-    <t>ALEXIS ISAI</t>
-  </si>
-  <si>
-    <t>DAVID</t>
-  </si>
-  <si>
-    <t>ROGELIO</t>
-  </si>
-  <si>
-    <t>LUIS ANGEL</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -776,7 +776,7 @@
         <v>6</v>
       </c>
       <c r="G4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H4">
         <v>7</v>
@@ -794,7 +794,7 @@
         <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -830,7 +830,7 @@
         <v>7</v>
       </c>
       <c r="Y4">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1007,7 +1007,7 @@
         <v>9</v>
       </c>
       <c r="G7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H7">
         <v>9</v>
@@ -1025,7 +1025,7 @@
         <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1061,7 +1061,7 @@
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>-1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1161,7 +1161,7 @@
         <v>10</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H9">
         <v>7</v>
@@ -1179,7 +1179,7 @@
         <v>8</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1215,7 +1215,7 @@
         <v>9</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1469,7 +1469,7 @@
         <v>8</v>
       </c>
       <c r="G13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H13">
         <v>7</v>
@@ -1487,7 +1487,7 @@
         <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1523,7 +1523,7 @@
         <v>7</v>
       </c>
       <c r="Y13">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1546,7 +1546,7 @@
         <v>6</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H14">
         <v>7</v>
@@ -1564,7 +1564,7 @@
         <v>6</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1600,7 +1600,7 @@
         <v>6</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1777,7 +1777,7 @@
         <v>6</v>
       </c>
       <c r="G17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H17">
         <v>8</v>
@@ -1795,7 +1795,7 @@
         <v>5</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1831,7 +1831,7 @@
         <v>5</v>
       </c>
       <c r="Y17">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2028,7 +2028,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2037,30 +2037,30 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>60</v>
+        <v>73.33</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>26.67</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>7.1</v>
       </c>
       <c r="I4">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J4">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2069,19 +2069,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E5">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="G5">
-        <v>26.67</v>
+        <v>6.67</v>
       </c>
       <c r="H5">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2161,7 +2161,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2186,126 +2186,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>21330051920135</v>
-      </c>
-      <c r="B2" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>21330051920140</v>
-      </c>
-      <c r="B3" t="s">
-        <v>47</v>
-      </c>
-      <c r="C3" t="s">
-        <v>53</v>
-      </c>
-      <c r="D3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>21330051920141</v>
-      </c>
-      <c r="B4" t="s">
-        <v>48</v>
-      </c>
-      <c r="C4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D4" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>21330051920395</v>
-      </c>
-      <c r="B5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C5" t="s">
-        <v>55</v>
-      </c>
-      <c r="D5" t="s">
-        <v>60</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>21330051920147</v>
-      </c>
-      <c r="B6" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D6" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>21330051920382</v>
-      </c>
-      <c r="B7" t="s">
-        <v>51</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>62</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>38</v>
       </c>
     </row>
   </sheetData>
@@ -2347,109 +2227,109 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>71</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920138</v>
       </c>
       <c r="B3" t="s">
         <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920139</v>
       </c>
       <c r="B4" t="s">
         <v>48</v>
       </c>
       <c r="C4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>73</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>21330051920395</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
         <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>74</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>21330051920147</v>
+        <v>21330051650295</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>75</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>21330051920382</v>
+        <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>21330051920138</v>
+        <v>21330051920143</v>
       </c>
       <c r="B8" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="C8" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="D8" t="s">
         <v>77</v>
@@ -2460,13 +2340,13 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>21330051920139</v>
+        <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
         <v>78</v>
@@ -2477,13 +2357,13 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>21330051650295</v>
+        <v>21330051920146</v>
       </c>
       <c r="B10" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="C10" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="D10" t="s">
         <v>79</v>
@@ -2494,13 +2374,13 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>21330051920143</v>
+        <v>21330051920395</v>
       </c>
       <c r="B11" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="D11" t="s">
         <v>80</v>
@@ -2511,13 +2391,13 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>21330051920145</v>
+        <v>21330051920147</v>
       </c>
       <c r="B12" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C12" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
       <c r="D12" t="s">
         <v>81</v>
@@ -2528,13 +2408,13 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>21330051920146</v>
+        <v>21330051920148</v>
       </c>
       <c r="B13" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
         <v>82</v>
@@ -2545,13 +2425,13 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>21330051920148</v>
+        <v>21330051920150</v>
       </c>
       <c r="B14" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="D14" t="s">
         <v>83</v>
@@ -2562,13 +2442,13 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>21330051920150</v>
+        <v>21330051920382</v>
       </c>
       <c r="B15" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="D15" t="s">
         <v>84</v>
@@ -2582,10 +2462,10 @@
         <v>21330051920392</v>
       </c>
       <c r="B16" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C16" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="D16" t="s">
         <v>85</v>
@@ -2601,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2633,16 +2513,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920140</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -2656,16 +2536,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>21330051920140</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C3" t="s">
         <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -2679,16 +2559,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920143</v>
+        <v>21330051920141</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -2702,16 +2582,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920148</v>
+        <v>21330051920141</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="D5" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -2720,6 +2600,98 @@
         <v>36</v>
       </c>
       <c r="G5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>21330051920145</v>
+      </c>
+      <c r="B6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" t="s">
+        <v>50</v>
+      </c>
+      <c r="D6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" t="s">
+        <v>6</v>
+      </c>
+      <c r="F6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>21330051920145</v>
+      </c>
+      <c r="B7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C7" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>21330051920143</v>
+      </c>
+      <c r="B8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>6</v>
+      </c>
+      <c r="F8" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>21330051920148</v>
+      </c>
+      <c r="B9" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -134,13 +134,13 @@
     <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Acevedo Rendón Ismael Arturo</t>
+  </si>
+  <si>
     <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Acevedo Rendón Ismael Arturo</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
@@ -806,7 +806,7 @@
         <v>-1</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R4">
         <v>-1</v>
@@ -824,7 +824,7 @@
         <v>5</v>
       </c>
       <c r="W4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X4">
         <v>7</v>
@@ -883,7 +883,7 @@
         <v>-1</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
         <v>-1</v>
@@ -960,7 +960,7 @@
         <v>-1</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
         <v>-1</v>
@@ -1037,7 +1037,7 @@
         <v>-1</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R7">
         <v>-1</v>
@@ -1114,7 +1114,7 @@
         <v>-1</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
         <v>-1</v>
@@ -1191,7 +1191,7 @@
         <v>-1</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
         <v>-1</v>
@@ -1209,7 +1209,7 @@
         <v>5</v>
       </c>
       <c r="W9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X9">
         <v>9</v>
@@ -1268,7 +1268,7 @@
         <v>-1</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
         <v>-1</v>
@@ -1345,7 +1345,7 @@
         <v>-1</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R11">
         <v>-1</v>
@@ -1422,7 +1422,7 @@
         <v>-1</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
         <v>-1</v>
@@ -1499,7 +1499,7 @@
         <v>-1</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R13">
         <v>-1</v>
@@ -1576,7 +1576,7 @@
         <v>-1</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R14">
         <v>-1</v>
@@ -1594,7 +1594,7 @@
         <v>5</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>6</v>
@@ -1653,7 +1653,7 @@
         <v>-1</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
         <v>-1</v>
@@ -1730,7 +1730,7 @@
         <v>-1</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R16">
         <v>-1</v>
@@ -1748,7 +1748,7 @@
         <v>9</v>
       </c>
       <c r="W16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X16">
         <v>10</v>
@@ -1807,7 +1807,7 @@
         <v>-1</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R17">
         <v>-1</v>
@@ -1825,7 +1825,7 @@
         <v>5</v>
       </c>
       <c r="W17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X17">
         <v>5</v>
@@ -1884,7 +1884,7 @@
         <v>-1</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R18">
         <v>-1</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2037,19 +2037,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>73.33</v>
+        <v>93.33</v>
       </c>
       <c r="G4">
-        <v>26.67</v>
+        <v>6.67</v>
       </c>
       <c r="H4">
-        <v>7.1</v>
+        <v>7.7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2081,7 +2081,7 @@
         <v>6.67</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -2113,7 +2113,7 @@
         <v>6.67</v>
       </c>
       <c r="H6">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2481,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2513,16 +2513,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
@@ -2536,16 +2536,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920140</v>
+        <v>21330051920135</v>
       </c>
       <c r="B3" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
@@ -2559,16 +2559,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
@@ -2582,16 +2582,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C5" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
@@ -2605,16 +2605,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C6" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
@@ -2628,16 +2628,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>7</v>
@@ -2651,16 +2651,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920143</v>
+        <v>21330051920145</v>
       </c>
       <c r="B8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
@@ -2674,16 +2674,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920148</v>
+        <v>21330051920145</v>
       </c>
       <c r="B9" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>7</v>
@@ -2692,6 +2692,98 @@
         <v>36</v>
       </c>
       <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>21330051920147</v>
+      </c>
+      <c r="B10" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D10" t="s">
+        <v>81</v>
+      </c>
+      <c r="E10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F10" t="s">
+        <v>37</v>
+      </c>
+      <c r="G10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>21330051920147</v>
+      </c>
+      <c r="B11" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" t="s">
+        <v>67</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>21330051920143</v>
+      </c>
+      <c r="B12" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" t="s">
+        <v>64</v>
+      </c>
+      <c r="D12" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" t="s">
+        <v>6</v>
+      </c>
+      <c r="F12" t="s">
+        <v>37</v>
+      </c>
+      <c r="G12">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>21330051920148</v>
+      </c>
+      <c r="B13" t="s">
+        <v>56</v>
+      </c>
+      <c r="C13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D13" t="s">
+        <v>82</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -137,13 +137,13 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
+    <t>Martínez Castillo Columba</t>
+  </si>
+  <si>
     <t>Acevedo Rendón Ismael Arturo</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
-  </si>
-  <si>
-    <t>Martínez Castillo Columba</t>
   </si>
   <si>
     <t>NC</t>
@@ -809,7 +809,7 @@
         <v>7</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
         <v>-1</v>
@@ -827,7 +827,7 @@
         <v>6</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
         <v>6</v>
@@ -886,7 +886,7 @@
         <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
         <v>-1</v>
@@ -963,7 +963,7 @@
         <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S6">
         <v>-1</v>
@@ -981,7 +981,7 @@
         <v>9</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y6">
         <v>9</v>
@@ -1040,7 +1040,7 @@
         <v>7</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S7">
         <v>-1</v>
@@ -1058,7 +1058,7 @@
         <v>6</v>
       </c>
       <c r="X7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y7">
         <v>8</v>
@@ -1117,7 +1117,7 @@
         <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
         <v>-1</v>
@@ -1135,7 +1135,7 @@
         <v>9</v>
       </c>
       <c r="X8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y8">
         <v>10</v>
@@ -1194,7 +1194,7 @@
         <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S9">
         <v>-1</v>
@@ -1271,7 +1271,7 @@
         <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S10">
         <v>-1</v>
@@ -1348,7 +1348,7 @@
         <v>7</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S11">
         <v>-1</v>
@@ -1366,7 +1366,7 @@
         <v>6</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y11">
         <v>8</v>
@@ -1425,7 +1425,7 @@
         <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
         <v>-1</v>
@@ -1502,7 +1502,7 @@
         <v>5</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S13">
         <v>-1</v>
@@ -1520,7 +1520,7 @@
         <v>5</v>
       </c>
       <c r="X13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y13">
         <v>5</v>
@@ -1579,7 +1579,7 @@
         <v>7</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
         <v>-1</v>
@@ -1597,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="X14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y14">
         <v>6</v>
@@ -1656,7 +1656,7 @@
         <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
         <v>-1</v>
@@ -1674,7 +1674,7 @@
         <v>8</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y15">
         <v>8</v>
@@ -1733,7 +1733,7 @@
         <v>10</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S16">
         <v>-1</v>
@@ -1810,7 +1810,7 @@
         <v>7</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S17">
         <v>-1</v>
@@ -1828,7 +1828,7 @@
         <v>6</v>
       </c>
       <c r="X17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y17">
         <v>7</v>
@@ -1887,7 +1887,7 @@
         <v>10</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S18">
         <v>-1</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2081,7 +2081,7 @@
         <v>6.67</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2092,7 +2092,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>40</v>
@@ -2101,19 +2101,19 @@
         <v>15</v>
       </c>
       <c r="D6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="G6">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.4</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -2124,7 +2124,7 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>41</v>
@@ -2145,7 +2145,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -2481,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2743,16 +2743,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920143</v>
+        <v>21330051920382</v>
       </c>
       <c r="B12" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="C12" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -2766,16 +2766,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920148</v>
+        <v>21330051920382</v>
       </c>
       <c r="B13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C13" t="s">
-        <v>68</v>
+        <v>50</v>
       </c>
       <c r="D13" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -2784,6 +2784,52 @@
         <v>36</v>
       </c>
       <c r="G13">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>21330051920143</v>
+      </c>
+      <c r="B14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C14" t="s">
+        <v>64</v>
+      </c>
+      <c r="D14" t="s">
+        <v>77</v>
+      </c>
+      <c r="E14" t="s">
+        <v>6</v>
+      </c>
+      <c r="F14" t="s">
+        <v>37</v>
+      </c>
+      <c r="G14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>21330051920148</v>
+      </c>
+      <c r="B15" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D15" t="s">
+        <v>82</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -812,7 +812,7 @@
         <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
         <v>7</v>
@@ -889,7 +889,7 @@
         <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T5">
         <v>10</v>
@@ -966,7 +966,7 @@
         <v>8</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T6">
         <v>9</v>
@@ -984,7 +984,7 @@
         <v>9</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1043,7 +1043,7 @@
         <v>8</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T7">
         <v>10</v>
@@ -1061,7 +1061,7 @@
         <v>9</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1120,7 +1120,7 @@
         <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T8">
         <v>10</v>
@@ -1138,7 +1138,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1197,7 +1197,7 @@
         <v>10</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T9">
         <v>7</v>
@@ -1274,7 +1274,7 @@
         <v>10</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T10">
         <v>7</v>
@@ -1292,7 +1292,7 @@
         <v>10</v>
       </c>
       <c r="Y10">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1351,7 +1351,7 @@
         <v>8</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T11">
         <v>6</v>
@@ -1369,7 +1369,7 @@
         <v>9</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1428,7 +1428,7 @@
         <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T12">
         <v>10</v>
@@ -1446,7 +1446,7 @@
         <v>10</v>
       </c>
       <c r="Y12">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1505,7 +1505,7 @@
         <v>5</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T13">
         <v>8</v>
@@ -1582,7 +1582,7 @@
         <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T14">
         <v>6</v>
@@ -1600,7 +1600,7 @@
         <v>7</v>
       </c>
       <c r="Y14">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1659,7 +1659,7 @@
         <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T15">
         <v>9</v>
@@ -1677,7 +1677,7 @@
         <v>9</v>
       </c>
       <c r="Y15">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1736,7 +1736,7 @@
         <v>10</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
         <v>10</v>
@@ -1754,7 +1754,7 @@
         <v>10</v>
       </c>
       <c r="Y16">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1813,7 +1813,7 @@
         <v>7</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T17">
         <v>7</v>
@@ -1890,7 +1890,7 @@
         <v>10</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T18">
         <v>10</v>
@@ -1908,7 +1908,7 @@
         <v>10</v>
       </c>
       <c r="Y18">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2037,19 +2037,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>93.33</v>
+        <v>86.67</v>
       </c>
       <c r="G4">
-        <v>6.67</v>
+        <v>13.33</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2481,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2697,16 +2697,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D10" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
@@ -2720,16 +2720,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>21330051920147</v>
+        <v>21330051920382</v>
       </c>
       <c r="B11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C11" t="s">
-        <v>67</v>
+        <v>50</v>
       </c>
       <c r="D11" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="E11" t="s">
         <v>7</v>
@@ -2743,16 +2743,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>21330051920382</v>
+        <v>21330051920143</v>
       </c>
       <c r="B12" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
         <v>6</v>
@@ -2766,16 +2766,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>21330051920382</v>
+        <v>21330051920148</v>
       </c>
       <c r="B13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C13" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="D13" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>7</v>
@@ -2784,52 +2784,6 @@
         <v>36</v>
       </c>
       <c r="G13">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>21330051920143</v>
-      </c>
-      <c r="B14" t="s">
-        <v>51</v>
-      </c>
-      <c r="C14" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" t="s">
-        <v>37</v>
-      </c>
-      <c r="G14">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>21330051920148</v>
-      </c>
-      <c r="B15" t="s">
-        <v>56</v>
-      </c>
-      <c r="C15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" t="s">
-        <v>82</v>
-      </c>
-      <c r="E15" t="s">
-        <v>7</v>
-      </c>
-      <c r="F15" t="s">
-        <v>36</v>
-      </c>
-      <c r="G15">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -797,7 +797,7 @@
         <v>7</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O4">
         <v>-1</v>
@@ -815,7 +815,7 @@
         <v>6</v>
       </c>
       <c r="T4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U4">
         <v>5</v>
@@ -874,7 +874,7 @@
         <v>10</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
         <v>-1</v>
@@ -892,7 +892,7 @@
         <v>8</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>9</v>
@@ -951,7 +951,7 @@
         <v>9</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
         <v>-1</v>
@@ -1028,7 +1028,7 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
         <v>-1</v>
@@ -1105,7 +1105,7 @@
         <v>10</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
         <v>-1</v>
@@ -1182,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O9">
         <v>-1</v>
@@ -1259,7 +1259,7 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O10">
         <v>-1</v>
@@ -1277,7 +1277,7 @@
         <v>6</v>
       </c>
       <c r="T10">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U10">
         <v>5</v>
@@ -1336,7 +1336,7 @@
         <v>5</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
         <v>-1</v>
@@ -1354,7 +1354,7 @@
         <v>5</v>
       </c>
       <c r="T11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U11">
         <v>5</v>
@@ -1413,7 +1413,7 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O12">
         <v>-1</v>
@@ -1431,7 +1431,7 @@
         <v>7</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>6</v>
@@ -1490,7 +1490,7 @@
         <v>5</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O13">
         <v>-1</v>
@@ -1508,7 +1508,7 @@
         <v>5</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U13">
         <v>7</v>
@@ -1567,7 +1567,7 @@
         <v>7</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
         <v>-1</v>
@@ -1644,7 +1644,7 @@
         <v>10</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O15">
         <v>-1</v>
@@ -1662,7 +1662,7 @@
         <v>6</v>
       </c>
       <c r="T15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U15">
         <v>6</v>
@@ -1721,7 +1721,7 @@
         <v>10</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O16">
         <v>-1</v>
@@ -1739,7 +1739,7 @@
         <v>6</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
         <v>9</v>
@@ -1798,7 +1798,7 @@
         <v>8</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O17">
         <v>-1</v>
@@ -1816,7 +1816,7 @@
         <v>7</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U17">
         <v>5</v>
@@ -1875,7 +1875,7 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O18">
         <v>-1</v>
@@ -1893,7 +1893,7 @@
         <v>7</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U18">
         <v>8</v>
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>0</v>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -128,10 +128,10 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>González Sánchez Rene Aurelio</t>
+  </si>
+  <si>
     <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>González Sánchez Rene Aurelio</t>
   </si>
   <si>
     <t>Hernández Mendoza Delfina</t>
@@ -803,7 +803,7 @@
         <v>-1</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
         <v>7</v>
@@ -821,7 +821,7 @@
         <v>5</v>
       </c>
       <c r="V4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W4">
         <v>6</v>
@@ -880,7 +880,7 @@
         <v>-1</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
         <v>9</v>
@@ -957,7 +957,7 @@
         <v>-1</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q6">
         <v>9</v>
@@ -1034,7 +1034,7 @@
         <v>-1</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q7">
         <v>7</v>
@@ -1052,7 +1052,7 @@
         <v>5</v>
       </c>
       <c r="V7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W7">
         <v>6</v>
@@ -1111,7 +1111,7 @@
         <v>-1</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q8">
         <v>9</v>
@@ -1188,7 +1188,7 @@
         <v>-1</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q9">
         <v>9</v>
@@ -1206,7 +1206,7 @@
         <v>5</v>
       </c>
       <c r="V9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1265,7 +1265,7 @@
         <v>-1</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q10">
         <v>9</v>
@@ -1342,7 +1342,7 @@
         <v>-1</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q11">
         <v>7</v>
@@ -1419,7 +1419,7 @@
         <v>-1</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q12">
         <v>9</v>
@@ -1496,7 +1496,7 @@
         <v>-1</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q13">
         <v>5</v>
@@ -1573,7 +1573,7 @@
         <v>-1</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q14">
         <v>7</v>
@@ -1650,7 +1650,7 @@
         <v>-1</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q15">
         <v>9</v>
@@ -1668,7 +1668,7 @@
         <v>6</v>
       </c>
       <c r="V15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="W15">
         <v>8</v>
@@ -1727,7 +1727,7 @@
         <v>-1</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q16">
         <v>10</v>
@@ -1804,7 +1804,7 @@
         <v>-1</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q17">
         <v>7</v>
@@ -1881,7 +1881,7 @@
         <v>-1</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="Q18">
         <v>10</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -1973,19 +1973,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2">
+        <v>53.33</v>
+      </c>
+      <c r="G2">
         <v>46.67</v>
       </c>
-      <c r="G2">
-        <v>53.33</v>
-      </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -2005,19 +2005,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="G3">
-        <v>46.67</v>
+        <v>26.67</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2481,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2513,22 +2513,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E2" t="s">
         <v>6</v>
       </c>
       <c r="F2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -2536,22 +2536,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920135</v>
+        <v>21330051920145</v>
       </c>
       <c r="B3" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="C3" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="E3" t="s">
         <v>7</v>
       </c>
       <c r="F3" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -2559,22 +2559,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B4" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C4" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
         <v>6</v>
       </c>
       <c r="F4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -2582,22 +2582,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>21330051920140</v>
+        <v>21330051920382</v>
       </c>
       <c r="B5" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G5">
         <v>5</v>
@@ -2605,22 +2605,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>21330051920141</v>
+        <v>21330051920135</v>
       </c>
       <c r="B6" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>6</v>
       </c>
       <c r="F6" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -2628,19 +2628,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>21330051920141</v>
+        <v>21330051920140</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -2651,22 +2651,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>21330051920145</v>
+        <v>21330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="D8" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E8" t="s">
         <v>6</v>
       </c>
       <c r="F8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G8">
         <v>5</v>
@@ -2674,116 +2674,24 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>21330051920145</v>
+        <v>21330051920143</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F9" t="s">
         <v>36</v>
       </c>
       <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>21330051920382</v>
-      </c>
-      <c r="B10" t="s">
-        <v>57</v>
-      </c>
-      <c r="C10" t="s">
-        <v>50</v>
-      </c>
-      <c r="D10" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G10">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>21330051920382</v>
-      </c>
-      <c r="B11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" t="s">
-        <v>84</v>
-      </c>
-      <c r="E11" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>21330051920143</v>
-      </c>
-      <c r="B12" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" t="s">
-        <v>64</v>
-      </c>
-      <c r="D12" t="s">
-        <v>77</v>
-      </c>
-      <c r="E12" t="s">
-        <v>6</v>
-      </c>
-      <c r="F12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>21330051920148</v>
-      </c>
-      <c r="B13" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" t="s">
-        <v>68</v>
-      </c>
-      <c r="D13" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ASV - Estadisticos 20221.xlsx
+++ b/grupos/3ASV - Estadisticos 20221.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="86">
   <si>
     <t>Materia</t>
   </si>
@@ -128,16 +128,16 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Villanueva Morales Luis Arturo</t>
+  </si>
+  <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Rodriguez Roman Marisol</t>
+  </si>
+  <si>
     <t>González Sánchez Rene Aurelio</t>
-  </si>
-  <si>
-    <t>Villanueva Morales Luis Arturo</t>
-  </si>
-  <si>
-    <t>Hernández Mendoza Delfina</t>
-  </si>
-  <si>
-    <t>Rodriguez Roman Marisol</t>
   </si>
   <si>
     <t>Martínez Castillo Columba</t>
@@ -800,7 +800,7 @@
         <v>5</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P4">
         <v>8</v>
@@ -818,7 +818,7 @@
         <v>6</v>
       </c>
       <c r="U4">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4">
         <v>6</v>
@@ -877,7 +877,7 @@
         <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P5">
         <v>10</v>
@@ -954,7 +954,7 @@
         <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
         <v>7</v>
@@ -1031,7 +1031,7 @@
         <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
         <v>8</v>
@@ -1049,7 +1049,7 @@
         <v>10</v>
       </c>
       <c r="U7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V7">
         <v>6</v>
@@ -1108,7 +1108,7 @@
         <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P8">
         <v>8</v>
@@ -1185,7 +1185,7 @@
         <v>8</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P9">
         <v>7</v>
@@ -1203,7 +1203,7 @@
         <v>7</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>6</v>
@@ -1262,7 +1262,7 @@
         <v>10</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
         <v>8</v>
@@ -1280,7 +1280,7 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V10">
         <v>7</v>
@@ -1339,7 +1339,7 @@
         <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
         <v>5</v>
@@ -1357,7 +1357,7 @@
         <v>7</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>5</v>
@@ -1416,7 +1416,7 @@
         <v>8</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P12">
         <v>8</v>
@@ -1434,7 +1434,7 @@
         <v>9</v>
       </c>
       <c r="U12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>8</v>
@@ -1493,7 +1493,7 @@
         <v>5</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P13">
         <v>5</v>
@@ -1570,7 +1570,7 @@
         <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P14">
         <v>5</v>
@@ -1588,7 +1588,7 @@
         <v>6</v>
       </c>
       <c r="U14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V14">
         <v>5</v>
@@ -1647,7 +1647,7 @@
         <v>8</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P15">
         <v>7</v>
@@ -1724,7 +1724,7 @@
         <v>8</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P16">
         <v>9</v>
@@ -1801,7 +1801,7 @@
         <v>5</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P17">
         <v>5</v>
@@ -1819,7 +1819,7 @@
         <v>6</v>
       </c>
       <c r="U17">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V17">
         <v>5</v>
@@ -1878,7 +1878,7 @@
         <v>8</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
         <v>6</v>
@@ -1964,7 +1964,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
         <v>36</v>
@@ -1973,19 +1973,19 @@
         <v>15</v>
       </c>
       <c r="D2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>53.33</v>
+        <v>73.33</v>
       </c>
       <c r="G2">
-        <v>46.67</v>
+        <v>26.67</v>
       </c>
       <c r="H2">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -1996,7 +1996,7 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>37</v>
@@ -2005,19 +2005,19 @@
         <v>15</v>
       </c>
       <c r="D3">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>73.33</v>
+        <v>86.67</v>
       </c>
       <c r="G3">
-        <v>26.67</v>
+        <v>13.33</v>
       </c>
       <c r="H3">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -2028,7 +2028,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>38</v>
@@ -2037,19 +2037,19 @@
         <v>15</v>
       </c>
       <c r="D4">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>86.67</v>
+        <v>93.33</v>
       </c>
       <c r="G4">
-        <v>13.33</v>
+        <v>6.67</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.5</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -2060,7 +2060,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>39</v>
@@ -2069,19 +2069,19 @@
         <v>15</v>
       </c>
       <c r="D5">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>93.33</v>
+        <v>100</v>
       </c>
       <c r="G5">
-        <v>6.67</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -2481,7 +2481,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -2513,19 +2513,19 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920145</v>
+        <v>21330051920147</v>
       </c>
       <c r="B2" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="s">
         <v>36</v>
@@ -2536,19 +2536,19 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>21330051920145</v>
+        <v>21330051920147</v>
       </c>
       <c r="B3" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="E3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
         <v>37</v>
@@ -2559,19 +2559,19 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>21330051920382</v>
+        <v>21330051920145</v>
       </c>
       <c r="B4" t="s">
-        <v>57</v>
+        <v>52</v>
       </c>
       <c r="C4" t="s">
         <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -2597,101 +2597,9 @@
         <v>7</v>
       </c>
       <c r="F5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>21330051920135</v>
-      </c>
-      <c r="B6" t="s">
-        <v>46</v>
-      </c>
-      <c r="C6" t="s">
-        <v>59</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>6</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>21330051920140</v>
-      </c>
-      <c r="B7" t="s">
-        <v>49</v>
-      </c>
-      <c r="C7" t="s">
-        <v>48</v>
-      </c>
-      <c r="D7" t="s">
-        <v>74</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>21330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>50</v>
-      </c>
-      <c r="C8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" t="s">
-        <v>76</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>36</v>
-      </c>
-      <c r="G8">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>21330051920143</v>
-      </c>
-      <c r="B9" t="s">
-        <v>51</v>
-      </c>
-      <c r="C9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E9" t="s">
-        <v>6</v>
-      </c>
-      <c r="F9" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9">
         <v>5</v>
       </c>
     </row>
